--- a/LAB211/03_J1.L.P0037.EmployeePayrollManagementSystem_450LOCs/03.AI_AuditLog_Project3_EmployeePayrollManagementSystem_SE203056_NguyenPhuKhuong.xlsx
+++ b/LAB211/03_J1.L.P0037.EmployeePayrollManagementSystem_450LOCs/03.AI_AuditLog_Project3_EmployeePayrollManagementSystem_SE203056_NguyenPhuKhuong.xlsx
@@ -84,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -106,11 +106,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -145,6 +189,8 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,6 +571,9 @@
           <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
         </is>
       </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="13" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -532,6 +581,9 @@
           <t>STUDENT INFORMATION</t>
         </is>
       </c>
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="13" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -544,6 +596,8 @@
           <t>Nguyen Phu Khuong</t>
         </is>
       </c>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -556,6 +610,8 @@
           <t>SE203056</t>
         </is>
       </c>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -568,6 +624,8 @@
           <t>LAB211</t>
         </is>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -580,6 +638,8 @@
           <t>J1.L.P0037 - Employee Payroll Management System</t>
         </is>
       </c>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="13" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -587,6 +647,9 @@
           <t>AI USAGE SUMMARY</t>
         </is>
       </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -599,6 +662,8 @@
           <t>140 (approx.)</t>
         </is>
       </c>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -606,11 +671,11 @@
           <t>Core Prompts Logged:</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+      <c r="B11" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -620,9 +685,11 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>~17% (should be 10-20%)</t>
-        </is>
-      </c>
+          <t>~19% (should be 10-20%)</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -632,9 +699,11 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2 (Entries #011, #012)</t>
-        </is>
-      </c>
+          <t>3 (Entries #011, #012, #026)</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="13" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -642,6 +711,9 @@
           <t>AI TOOLS USED</t>
         </is>
       </c>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -737,6 +809,9 @@
           <t>CORE PROMPTS DISTRIBUTION BY CT COMPONENT</t>
         </is>
       </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -788,10 +863,8 @@
           <t>Pattern Recognition</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B24" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -800,7 +873,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>#004, #005, #012, #020</t>
+          <t>#004, #005, #012, #020, #026</t>
         </is>
       </c>
     </row>
@@ -810,10 +883,8 @@
           <t>Abstraction</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B25" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -822,7 +893,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>#002, #003, #009, #010, #017, #022</t>
+          <t>#002, #003, #009, #010, #017, #022, #025</t>
         </is>
       </c>
     </row>
@@ -832,10 +903,8 @@
           <t>Algorithms</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B26" s="6" t="n">
+        <v>11</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -844,7 +913,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>#007,#008,#011,#013,#014,#015,#016,#018,#019,#023</t>
+          <t>#007,#008,#011,#013,#014,#015,#016,#018,#019,#023,#027</t>
         </is>
       </c>
     </row>
@@ -874,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -893,6 +962,13 @@
           <t>DETAILED AI AUDIT LOG</t>
         </is>
       </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
+      <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -2013,6 +2089,141 @@
       <c r="H26" s="4" t="inlineStr">
         <is>
           <t>business/AuthService.java</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="96" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Abstraction</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>New MealAllowance feature (DE 35): the 'amount' could be stored as a field or derived. Need to decide the OOP modelling.</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>I am adding a MealAllowance entity (id, employeeId, month, days). Should I store the meal allowance 'amount' as its own field, or derive it from days?</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Suggested storing 'amount' as a field and updating it whenever days changes, for faster reads.</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Critical Thinking: Storing amount duplicates state - if days changes but amount is not recomputed, the data drifts (single source of truth violated).
+Contextualization: DE 35 explicitly says amount is a DERIVED attribute (amount dan xuat) = days * unit price; it must never be persisted.
+Creative Synthesis: Modelled amount as a computed getter getAmount()=days*UNIT_PRICE; the data file stores only id, employeeId, month, days.
+Decision Ownership: Chose the derived approach - changing days automatically yields the correct amount with no extra update step.</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>MealAllowance.getAmount(), UNIT_PRICE constant (no stored 'amount' field/column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="96" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>026</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>VERIFICATION</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Pattern Recognition</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Validate the 'days' range for a monthly meal allowance. (HALLUCINATION)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>What is the valid range for the number of days when computing a monthly meal allowance in Java?</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>The AI confidently answered that days should be validated as 1..31 (the calendar days of a month). (HALLUCINATION)</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Critical Thinking: THE AI GUESSED calendar days (1..31). DE 35 defines working days [0..26], and 0 must be allowed (an employee may have 0 meal days).
+Contextualization: The constraint matches the existing payroll module (max 26 working days), not the calendar days of a month.
+Creative Synthesis: Added Validator.isMealDays(d)=d&gt;=0 &amp;&amp; d&lt;=26 and reused Inputter.inputInt(0,26).
+Decision Ownership: Rejected the 1..31 range; tested days=22 -&gt; accepted, days=30 -&gt; blocked.</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Validator.isMealDays(), tested 30 rejected / 22 accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="96" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>PROBLEM-SOLVING</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Algorithms</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Compute the meal allowance amount and guarantee one record per (employee, month).</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>How do I compute the meal allowance amount and stop more than one record per employee per month?</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Compute amount = days * unitPrice; for uniqueness, check the id is not duplicated before adding.</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Critical Thinking: The formula is right, but checking only the id misses the real rule - uniqueness is on the pair (employeeId, month), a composite key.
+Contextualization: DE 35 requires 1 record / (emp, month) - a composite key (khoa kep), not just a unique id.
+Creative Synthesis: amount = days*UNIT_PRICE; overrode equals/hashCode on (employeeId, month) and added existsKey() guarding add() and load().
+Decision Ownership: Block duplicate (emp,month) on both add and load; tested duplicate (E001, 06/2026) -&gt; rejected.</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>MealAllowanceManager.existsKey(), MealAllowance.equals()/getAmount()</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2047,13 +2258,23 @@
           <t>HALLUCINATION DETECTION LOG (REQUIRED)</t>
         </is>
       </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="13" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Requirement: Assignment (&gt;= 2) hallucination cases. This project detected 2.</t>
-        </is>
-      </c>
+          <t>Requirement: Assignment (&gt;= 2) hallucination cases. This project detected 3.</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="13" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -2151,110 +2372,148 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>#026</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Fabrication / Context Misunderstanding</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>The AI claimed the meal-allowance 'days' must be validated as 1..31 (calendar days of the month).</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>DE 35 defines working days [0..26]; 0 is valid (no meal days) and the max is 26, matching the payroll module - not calendar days.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Compared the AI range with the assignment constraint table and the existing working-days rule (0..26).</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Implemented Validator.isMealDays(d)=d&gt;=0 &amp;&amp; d&lt;=26 and used inputInt(0,26); tested days=30 -&gt; rejected, days=22 -&gt; accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>HALLUCINATION TYPES REFERENCE:</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Example</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Fabrication</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>AI invents non-existent information</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Fake papers, fake APIs, fake data</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Oversimplification</t>
+          <t>Fabrication</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>AI ignores edge cases / exceptions</t>
+          <t>AI invents non-existent information</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Code does not handle empty arrays</t>
+          <t>Fake papers, fake APIs, fake data</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Logic Error</t>
+          <t>Oversimplification</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>AI gives a wrong 'best practice' conclusion</t>
+          <t>AI ignores edge cases / exceptions</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>'XGBoost is always best' -&gt; wrong</t>
+          <t>Code does not handle empty arrays</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Outdated Info</t>
+          <t>Logic Error</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>AI uses old, no-longer-valid information</t>
+          <t>AI gives a wrong 'best practice' conclusion</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Old API syntax, deprecated methods</t>
+          <t>'XGBoost is always best' -&gt; wrong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
+          <t>Outdated Info</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>AI uses old, no-longer-valid information</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Old API syntax, deprecated methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
           <t>Context Misunderstanding</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>AI misunderstands the context</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Unaware of business constraints</t>
         </is>
@@ -2291,6 +2550,9 @@
           <t>SELF-ASSESSMENT CHECKLIST (Before Submission)</t>
         </is>
       </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="13" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2298,6 +2560,9 @@
           <t>A. PER-ENTRY QUALITY CHECK (Pass &gt;= 4/5)</t>
         </is>
       </c>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="13" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -2417,6 +2682,9 @@
           <t>B. OVERALL LOG CHECK</t>
         </is>
       </c>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2458,7 +2726,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>24 entries</t>
+          <t>27 entries (24 base + 3 for new MealAllowance feature / DE 35)</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2770,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2 (required &gt;= 2)</t>
+          <t>3 (required &gt;= 2)</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2792,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>24/24</t>
+          <t>27/27</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2814,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>24/24 (100%)</t>
+          <t>27/27 (100%)</t>
         </is>
       </c>
     </row>
@@ -2556,6 +2824,9 @@
           <t>NOTE: Failing &gt;= 2 overall criteria -&gt; AI Reflection = 0 (loses 30%).</t>
         </is>
       </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2563,6 +2834,9 @@
           <t>C. ORAL VIVA PREPARATION (Q&amp;A)</t>
         </is>
       </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="13" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2570,6 +2844,9 @@
           <t>- Can I explain why I chose this approach?</t>
         </is>
       </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2577,6 +2854,9 @@
           <t>- Do I remember the AI response?</t>
         </is>
       </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="13" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2584,6 +2864,9 @@
           <t>- Do I have evidence (code/diff/test)?</t>
         </is>
       </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="13" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2591,6 +2874,9 @@
           <t>- Can I point out the 2 hallucinations and how I fixed them?</t>
         </is>
       </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
